--- a/out/MLP-Mamba1_repeat_1_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.386393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.386393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.386393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.386393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.386393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.386393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.386393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.386393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001453085785242729</v>
+        <v>-0.0001385220495108515</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1669316476393649</v>
+        <v>-0.1591352292757827</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.386393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.862243845257878</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.862243845257878</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.1592737513252935</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1672019834645878</v>
+        <v>-0.1593936396756473</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4495692486006984</v>
+        <v>0.4310912044266653</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7328002176356699</v>
+        <v>0.7036164800762017</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03203171457307379</v>
+        <v>0.03071512121898311</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.986393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3465727987790734</v>
+        <v>0.333264073813149</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05617271347971925</v>
+        <v>0.05386398564748598</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.986393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4268760051809307</v>
+        <v>0.4102666003429957</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06824321293304215</v>
+        <v>0.06543838127547197</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5071847401887306</v>
+        <v>0.4872742520596483</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01805902900230547</v>
+        <v>0.01731647024398699</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4749718323772238</v>
+        <v>0.4563855941669298</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01003263353601213</v>
+        <v>0.009619901893906364</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.386393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4769609560230258</v>
+        <v>0.4582927593455245</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02107961179041162</v>
+        <v>0.02021362189083477</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.986393030374176</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.509100393912476</v>
+        <v>0.4891118489824992</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008278743590311163</v>
+        <v>0.007938431901878788</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5045597936152653</v>
+        <v>0.4847575796331705</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005894278162292831</v>
+        <v>0.005651062308233389</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5080661547789019</v>
+        <v>0.488119688631227</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002316993950025967</v>
+        <v>0.002221941566106775</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5068012732309438</v>
+        <v>0.4869063811817234</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001312908257793096</v>
+        <v>0.001258958796947765</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5071087427524608</v>
+        <v>0.4872010595532364</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004964556615010952</v>
+        <v>0.0004764913845795059</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5067888674166066</v>
+        <v>0.4868940730921505</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002306055348910609</v>
+        <v>0.0002206968909003153</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5067520909249936</v>
+        <v>0.4868586329950448</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.138380649587527e-05</v>
+        <v>7.734718002410539e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5066840553637373</v>
+        <v>0.4867932490328285</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.028024483792712e-05</v>
+        <v>1.932627333460911e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5066436271000837</v>
+        <v>0.4867541452041645</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>7.401629543134059e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5066386069947486</v>
+        <v>0.4867491258434716</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5066345889504049</v>
+        <v>0.486745071050636</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5066321542802141</v>
+        <v>0.4867424536472172</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5066266370382244</v>
+        <v>0.4867369364052275</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5066203130442165</v>
+        <v>0.4867306124112196</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5066149452556381</v>
+        <v>0.4867252446226412</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5066149820041298</v>
+        <v>0.4867252813711329</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5066150922496053</v>
+        <v>0.4867253916166085</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5066151657465889</v>
+        <v>0.4867254651135921</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5066153494890481</v>
+        <v>0.4867256488560512</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5066168929257046</v>
+        <v>0.4867271922927077</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5066183628653776</v>
+        <v>0.4867286622323808</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5066196123140997</v>
+        <v>0.4867299116811028</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.506620972008297</v>
+        <v>0.4867312713753001</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5066187670987877</v>
+        <v>0.4867290664657908</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5066183628653776</v>
+        <v>0.4867286622323808</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5066175176500657</v>
+        <v>0.4867278170170689</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.506618068877443</v>
+        <v>0.4867283682444461</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5066177381410165</v>
+        <v>0.4867280375080197</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.386393030374176</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5066174441530821</v>
+        <v>0.4867277435200852</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5066175176500657</v>
+        <v>0.4867278170170689</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.986393030374176</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5066170766681638</v>
+        <v>0.4867273760351669</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5066169664226882</v>
+        <v>0.4867272657896913</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.986393030374176</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5066169296741965</v>
+        <v>0.4867272290411996</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5066170766681638</v>
+        <v>0.4867273760351669</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5066165989377701</v>
+        <v>0.4867268983047733</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5066175543985574</v>
+        <v>0.4867278537655605</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5066175176500657</v>
+        <v>0.4867278170170689</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.986393030374176</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5066171869136393</v>
+        <v>0.4867274862806424</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5066176278955412</v>
+        <v>0.4867279272625444</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5066170031711802</v>
+        <v>0.4867273025381833</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5066168194287209</v>
+        <v>0.4867271187957241</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.506616415195311</v>
+        <v>0.4867267145623141</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.506615569979999</v>
+        <v>0.4867258693470021</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.386393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5066155332315073</v>
+        <v>0.4867258325985104</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5066156802254745</v>
+        <v>0.4867259795924777</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5066156067284909</v>
+        <v>0.486725906095494</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5066156802254745</v>
+        <v>0.4867259795924777</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5066157169739665</v>
+        <v>0.4867260163409696</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5066156067284909</v>
+        <v>0.486725906095494</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.862243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5066160477103928</v>
+        <v>0.486726347077396</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.862243845257878</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5066159374649173</v>
+        <v>0.4867262368319205</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5066159007164254</v>
+        <v>0.4867262000834285</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5066158272194418</v>
+        <v>0.4867261265864449</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5066157904709501</v>
+        <v>0.4867260898379532</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.711245132341913</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.506615569979999</v>
+        <v>0.4867258693470021</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.462243845257878</v>
+        <v>1.088844415955533</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5066154964830154</v>
+        <v>0.4867257958500185</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5066154229860318</v>
+        <v>0.4867257223530349</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.462243845257878</v>
+        <v>-1.111245132341913</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5066154597345237</v>
+        <v>0.4867257591015268</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5066153494890481</v>
+        <v>0.4867256488560512</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5066154597345237</v>
+        <v>0.4867257591015268</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.986393030374176</v>
+        <v>1.688844415955533</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5066157537224582</v>
+        <v>0.4867260530894613</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.1397082920398737</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.862243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.386393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001453085785242729</v>
+        <v>-0.0001151742376901675</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1669316476393649</v>
+        <v>-0.1323130778546159</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.862243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1670769562178892</v>
+        <v>-0.132428252092306</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1672019834645878</v>
+        <v>-0.1325295682709148</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4495692486006984</v>
+        <v>0.364309904469307</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7328002176356699</v>
+        <v>0.5967897290248519</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03203171457307379</v>
+        <v>0.02595700420441633</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3465727987790734</v>
+        <v>0.2838094398904126</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05617271347971925</v>
+        <v>0.04551961295548591</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4268760051809307</v>
+        <v>0.3488832560813231</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06824321293304215</v>
+        <v>0.05530095391728644</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5071847401887306</v>
+        <v>0.4139615872300106</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01805902900230547</v>
+        <v>0.01463401798282582</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4749718323772238</v>
+        <v>0.387857770614557</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01003263353601213</v>
+        <v>0.008128931766334974</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4769609560230258</v>
+        <v>0.3894687326317285</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02107961179041162</v>
+        <v>0.01708249826816544</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.509100393912476</v>
+        <v>0.4155138940675799</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008278743590311163</v>
+        <v>0.006707981099575259</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121086</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5045597936152653</v>
+        <v>0.4118333337682465</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005894278162292831</v>
+        <v>0.004774795259565331</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5080661547789019</v>
+        <v>0.4146738721607102</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002316993950025967</v>
+        <v>0.001877037201599994</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5068012732309438</v>
+        <v>0.4136477050113126</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001312908257793096</v>
+        <v>0.001063199324737562</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5071087427524608</v>
+        <v>0.4138959697813841</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004964556615010952</v>
+        <v>0.0004013317538158758</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5067888674166066</v>
+        <v>0.4136357551854029</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002306055348910609</v>
+        <v>0.0001854661567109978</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5067520909249936</v>
+        <v>0.4136049932162275</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.138380649587527e-05</v>
+        <v>6.523730060879578e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5066840553637373</v>
+        <v>0.4135487400028696</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.028024483792712e-05</v>
+        <v>1.551038732133709e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5066436271000837</v>
+        <v>0.4135149339141646</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>5.49368653649805e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5066386069947486</v>
+        <v>0.4135099175320396</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5066345889504049</v>
+        <v>0.4135057173227172</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5066321542802141</v>
+        <v>0.4135027334436115</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.862243845257878</v>
+        <v>-0.6369672081768307</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5066266370382244</v>
+        <v>0.4134972896986052</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5066203130442165</v>
+        <v>0.4134912969651748</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5066149452556381</v>
+        <v>0.4134859291765964</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5066149820041298</v>
+        <v>0.4134859659250881</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5066150922496053</v>
+        <v>0.4134860761705637</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5066151657465889</v>
+        <v>0.4134861496675473</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5066153494890481</v>
+        <v>0.4134863334100065</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5066168929257046</v>
+        <v>0.4134878768466629</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5066183628653776</v>
+        <v>0.413489346786336</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5066196123140997</v>
+        <v>0.413490596235058</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121086</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.506620972008297</v>
+        <v>0.4134919559292554</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5066187670987877</v>
+        <v>0.4134897510197461</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5066183628653776</v>
+        <v>0.413489346786336</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5066175176500657</v>
+        <v>0.4134885015710241</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.506618068877443</v>
+        <v>0.4134890527984013</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5066177381410165</v>
+        <v>0.4134887220619749</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5066174441530821</v>
+        <v>0.4134884280740405</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5066175176500657</v>
+        <v>0.4134885015710241</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5066170766681638</v>
+        <v>0.4134880605891221</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5066169664226882</v>
+        <v>0.4134879503436465</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5066169296741965</v>
+        <v>0.4134879135951549</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5066170766681638</v>
+        <v>0.4134880605891221</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5066165989377701</v>
+        <v>0.4134875828587285</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5066175543985574</v>
+        <v>0.4134885383195158</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5066175176500657</v>
+        <v>0.4134885015710241</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5066171869136393</v>
+        <v>0.4134881708345977</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5066176278955412</v>
+        <v>0.4134886118164996</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5066170031711802</v>
+        <v>0.4134879870921385</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5066168194287209</v>
+        <v>0.4134878033496793</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.506616415195311</v>
+        <v>0.4134873991162693</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.506615569979999</v>
+        <v>0.4134865539009573</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5066155332315073</v>
+        <v>0.4134865171524656</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5066156802254745</v>
+        <v>0.4134866641464329</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5066156067284909</v>
+        <v>0.4134865906494493</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5066156802254745</v>
+        <v>0.4134866641464329</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5066157169739665</v>
+        <v>0.4134867008949248</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5066156067284909</v>
+        <v>0.4134865906494493</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5066160477103928</v>
+        <v>0.4134870316313512</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.862243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5066159374649173</v>
+        <v>0.4134869213858757</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5066159007164254</v>
+        <v>0.4134868846373838</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5066158272194418</v>
+        <v>0.4134868111404001</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5066157904709501</v>
+        <v>0.4134867743919085</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.506615569979999</v>
+        <v>0.4134865539009573</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5066154964830154</v>
+        <v>0.4134864804039737</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5066154229860318</v>
+        <v>0.4134864069069901</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5066154597345237</v>
+        <v>0.413486443655482</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5066153494890481</v>
+        <v>0.4134863334100065</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5066154597345237</v>
+        <v>0.413486443655482</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5066157537224582</v>
+        <v>0.4134867376434165</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4853996634483337</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.1397082920398737</v>
+        <v>0.2599999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5426979660987854</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.4652667921121084</v>
+        <v>0.04999999999999971</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.6432117223739624</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.499316543340683</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4154578745365143</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.461862325668335</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.5039665699005127</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4190720915794373</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.486798882484436</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4444659650325775</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.5466374158859253</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4697518646717072</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.518916130065918</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4825779497623444</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5475355386734009</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.395593136548996</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4448360502719879</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4495954811573029</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4805828332901001</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.5032089352607727</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4514065384864807</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6652667921121085</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5333348512649536</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4905703067779541</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5795919895172119</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4474537074565887</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5275024771690369</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.47995525598526</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5434213280677795</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.5572196841239929</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.316383792256578</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5764630436897278</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.316383792256578</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.7113378047943115</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3874998688697815</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.5709226131439209</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5526131391525269</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4652667921121084</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4248546957969666</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4652667921121084</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.6080721020698547</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4589702188968658</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4991689324378967</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.620232105255127</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4652667921121084</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5676478743553162</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.316383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.588261604309082</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.316383792256578</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6124813556671143</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.316383792256578</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.7303333282470703</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.316383792256578</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6225461959838867</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001151742376901675</v>
+        <v>-0.0001164229180378607</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1323130778546159</v>
+        <v>-0.1337475717430304</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.2004249393939972</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.6198075413703918</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.2916108369827271</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4630562663078308</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.3592241406440735</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4717602133750916</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3867619335651398</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5618375539779663</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4443939626216888</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.01414979196763891</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4965183436870575</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4565982222557068</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4624841511249542</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1858502080323611</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.5484417080879211</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.132428252092306</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.6907597780227661</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1325295682709148</v>
+        <v>-0.1339571626925724</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.364309904469307</v>
+        <v>0.3350110231442554</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3208149075508118</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5967897290248519</v>
+        <v>0.536708117028059</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02595700420441633</v>
+        <v>0.02386946506148003</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.586647093296051</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2838094398904126</v>
+        <v>0.2488986295543327</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04551961295548591</v>
+        <v>0.04185890888712493</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.6612476110458374</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3488832560813231</v>
+        <v>0.308739016472335</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05530095391728644</v>
+        <v>0.05085363079994749</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3785367608070374</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4139615872300106</v>
+        <v>0.3685833862877211</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01463401798282582</v>
+        <v>0.01345714485741973</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3834068775177002</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.387857770614557</v>
+        <v>0.344579118580813</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008128931766334974</v>
+        <v>0.007474797972668686</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.7982680797576904</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4652667921121084</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3894687326317285</v>
+        <v>0.3460600905431895</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01708249826816544</v>
+        <v>0.01570800896136375</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.6136885285377502</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.316383792256578</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4155138940675799</v>
+        <v>0.3700096102687053</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006707981099575259</v>
+        <v>0.006167842263130993</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.6938066482543945</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6652667921121086</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4118333337682465</v>
+        <v>0.3666247923279328</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004774795259565331</v>
+        <v>0.004390134724421676</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4217609763145447</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4146738721607102</v>
+        <v>0.369236373545107</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001877037201599994</v>
+        <v>0.001724953387329288</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.615000307559967</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1858502080323611</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4136477050113126</v>
+        <v>0.3682923574683182</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001063199324737562</v>
+        <v>0.0009768801873850318</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3822829127311707</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4138959697813841</v>
+        <v>0.3685203401408431</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004013317538158758</v>
+        <v>0.0003696237845874692</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.394900381565094</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4136357551854029</v>
+        <v>0.3682803799430712</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001854661567109978</v>
+        <v>0.0001700527105031714</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3066329061985016</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4136049932162275</v>
+        <v>0.3682516968097959</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.523730060879578e-05</v>
+        <v>5.958602354831795e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3134557604789734</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4135487400028696</v>
+        <v>0.3681995674182023</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.551038732133709e-05</v>
+        <v>1.407943006636009e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4371463656425476</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4135149339141646</v>
+        <v>0.3681680787184082</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.49368653649805e-06</v>
+        <v>4.539715033180046e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4199511408805847</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4135099175320396</v>
+        <v>0.3681630638255672</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.5379582643508911</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4135057173227172</v>
+        <v>0.3681587909080016</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3544570207595825</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.01414979196763891</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4135027334436115</v>
+        <v>0.3681556232864368</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.2801841199398041</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6369672081768307</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4134972896986052</v>
+        <v>0.368150253959449</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3297100961208344</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4134912969651748</v>
+        <v>0.3681442612260187</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4335220456123352</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4134859291765964</v>
+        <v>0.3681388934374403</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4176671802997589</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4134859659250881</v>
+        <v>0.368138930185932</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4761438965797424</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4134860761705637</v>
+        <v>0.3681390404314075</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4322766363620758</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1858502080323611</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4134861496675473</v>
+        <v>0.3681391139283912</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.7403702735900879</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4134863334100065</v>
+        <v>0.3681392976708503</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.8130124807357788</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.316383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4134878768466629</v>
+        <v>0.3681408411075068</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.7676755785942078</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.413489346786336</v>
+        <v>0.3681423110471799</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.8324552774429321</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.316383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.413490596235058</v>
+        <v>0.3681435604959019</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.960643470287323</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6652667921121086</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4134919559292554</v>
+        <v>0.3681449201900991</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.1918127834796906</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4134897510197461</v>
+        <v>0.3681427152805899</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.3517267405986786</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.413489346786336</v>
+        <v>0.3681423110471799</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4661435186862946</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4134885015710241</v>
+        <v>0.3681414658318679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3531458377838135</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4134890527984013</v>
+        <v>0.3681420170592452</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.356816291809082</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4134887220619749</v>
+        <v>0.3681416863228187</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.557966411113739</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4134884280740405</v>
+        <v>0.3681413923348842</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2605750560760498</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.6652667921121085</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4134885015710241</v>
+        <v>0.3681414658318679</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.5076971650123596</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4134880605891221</v>
+        <v>0.3681410248499659</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4337548613548279</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4134879503436465</v>
+        <v>0.3681409146044904</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.5529481768608093</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4134879135951549</v>
+        <v>0.3681408778559987</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.2589759230613708</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4134880605891221</v>
+        <v>0.3681410248499659</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.8536573052406311</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4134875828587285</v>
+        <v>0.3681405471195723</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.7089012861251831</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4134885383195158</v>
+        <v>0.3681415025803596</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3678160309791565</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4134885015710241</v>
+        <v>0.3681414658318679</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.5306645035743713</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.01414979196763891</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4134881708345977</v>
+        <v>0.3681411350954415</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3494357168674469</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4134886118164996</v>
+        <v>0.3681415760773434</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3034746646881104</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4134879870921385</v>
+        <v>0.3681409513529823</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3632876873016357</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4134878033496793</v>
+        <v>0.3681407676105232</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.1976531744003296</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4134873991162693</v>
+        <v>0.3681403633771131</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3733662664890289</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4134865539009573</v>
+        <v>0.3681395181618012</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5482906103134155</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4134865171524656</v>
+        <v>0.3681394814133095</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3889815509319305</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.16</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4134866641464329</v>
+        <v>0.3681396284072767</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4566836357116699</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4134865906494493</v>
+        <v>0.3681395549102931</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.6460220217704773</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4134866641464329</v>
+        <v>0.3681396284072767</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3199810683727264</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4134867008949248</v>
+        <v>0.3681396651557686</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.678239643573761</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4134865906494493</v>
+        <v>0.3681395549102931</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3479641377925873</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4134870316313512</v>
+        <v>0.368139995892195</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4870399236679077</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4134869213858757</v>
+        <v>0.3681398856467195</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3583871722221375</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4134868846373838</v>
+        <v>0.3681398488982275</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.3734100461006165</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4134868111404001</v>
+        <v>0.3681397754012439</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3255375027656555</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4134867743919085</v>
+        <v>0.3681397386527522</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.2875658273696899</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4134865539009573</v>
+        <v>0.3681395181618012</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4381441473960876</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4134864804039737</v>
+        <v>0.3681394446648175</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3869932591915131</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4134864069069901</v>
+        <v>0.3681393711678339</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3104011714458466</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.413486443655482</v>
+        <v>0.3681394079163258</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.5032430291175842</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4134863334100065</v>
+        <v>0.3681392976708503</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.6461470127105713</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.316383792256578</v>
+        <v>0.8600000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.413486443655482</v>
+        <v>0.3681394079163258</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.5852537155151367</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.316383792256578</v>
+        <v>1.280000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4134867376434165</v>
+        <v>0.3681397019042603</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000008.xlsx
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.486798882484436</v>
+        <v>0.4867988228797913</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.4905703067779541</v>
+        <v>0.4905702471733093</v>
       </c>
       <c r="JB24" t="n">
         <v>0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.7113378047943115</v>
+        <v>0.7113378643989563</v>
       </c>
       <c r="JB32" t="n">
         <v>0.5799999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.4991689324378967</v>
+        <v>0.499168872833252</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.16</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.6124813556671143</v>
+        <v>0.612481415271759</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.6938066482543945</v>
+        <v>0.6938067674636841</v>
       </c>
       <c r="JB67" t="n">
         <v>0.7199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.3822829127311707</v>
+        <v>0.382282942533493</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.8130124807357788</v>
+        <v>0.8130123615264893</v>
       </c>
       <c r="JB85" t="n">
         <v>0.7199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.1918127834796906</v>
+        <v>0.1918128132820129</v>
       </c>
       <c r="JB89" t="n">
         <v>0.16</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.4661435186862946</v>
+        <v>0.4661434888839722</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.3531458377838135</v>
+        <v>0.3531457781791687</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.4337548613548279</v>
+        <v>0.4337548017501831</v>
       </c>
       <c r="JB97" t="n">
         <v>0.16</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.2589759230613708</v>
+        <v>0.2589759528636932</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.7089012861251831</v>
+        <v>0.7089012265205383</v>
       </c>
       <c r="JB101" t="n">
         <v>0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.3678160309791565</v>
+        <v>0.3678160011768341</v>
       </c>
       <c r="JB102" t="n">
         <v>0.3</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.3199810683727264</v>
+        <v>0.3199810385704041</v>
       </c>
       <c r="JB113" t="n">
         <v>0.16</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.5852537155151367</v>
+        <v>0.5852537751197815</v>
       </c>
       <c r="JB126" t="n">
         <v>1.280000000000001</v>
